--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-prevision.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-prevision.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/prevision</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/prevision</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -299,6 +299,9 @@
 </t>
   </si>
   <si>
+    <t>Previsión y tramo FONASA</t>
+  </si>
+  <si>
     <t>An Extension</t>
   </si>
   <si>
@@ -346,7 +349,7 @@
 </t>
   </si>
   <si>
-    <t>identifies the meaning of the extension</t>
+    <t>Nombre de la subextensión</t>
   </si>
   <si>
     <t>Source of the definition for the extension code - a logical name or a URL.</t>
@@ -371,7 +374,7 @@
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
+    <t>Código de previsión (NID)</t>
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
@@ -411,11 +414,20 @@
     <t>Extension.extension:tramoFonasa.value[x]</t>
   </si>
   <si>
+    <t>Tramo FONASA A, B, C o D (NID)</t>
+  </si>
+  <si>
     <t>https://interoperabilidad.minsal.cl/fhir/ig/nid/ValueSet/VSTramosFONASA</t>
+  </si>
+  <si>
+    <t>URL que identifica la extensión</t>
   </si>
   <si>
     <t>base64Binary
 booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
   </si>
 </sst>
 </file>
@@ -1133,10 +1145,10 @@
         <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1175,19 +1187,19 @@
         <v>77</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1207,13 +1219,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>77</v>
@@ -1226,7 +1238,7 @@
         <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>77</v>
@@ -1241,7 +1253,7 @@
         <v>9</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1292,7 +1304,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1312,10 +1324,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1415,10 +1427,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1447,7 +1459,7 @@
         <v>31</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1486,19 +1498,19 @@
         <v>77</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1518,10 +1530,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1544,16 +1556,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1561,7 +1573,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>77</v>
@@ -1603,7 +1615,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>84</v>
@@ -1618,15 +1630,15 @@
         <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1649,13 +1661,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1682,11 +1694,11 @@
         <v>77</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y9" s="2"/>
       <c r="Z9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>77</v>
@@ -1704,7 +1716,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -1716,21 +1728,21 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -1743,7 +1755,7 @@
         <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>77</v>
@@ -1755,10 +1767,10 @@
         <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1809,7 +1821,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -1829,10 +1841,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1932,10 +1944,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1964,7 +1976,7 @@
         <v>31</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2003,19 +2015,19 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2035,10 +2047,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2061,16 +2073,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2078,7 +2090,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>77</v>
@@ -2120,7 +2132,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>84</v>
@@ -2135,15 +2147,15 @@
         <v>77</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2166,13 +2178,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2199,11 +2211,11 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -2221,7 +2233,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2233,18 +2245,18 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2267,16 +2279,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2326,7 +2338,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>84</v>
@@ -2341,15 +2353,15 @@
         <v>77</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2372,13 +2384,13 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2429,7 +2441,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2441,10 +2453,10 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-prevision.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-prevision.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
